--- a/data/trans_dic/IP31KM02_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_R_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>69,16%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,3; 78,47</t>
+          <t>58,43; 79,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54,48; 77,0</t>
+          <t>57,25; 79,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,18; 74,86</t>
+          <t>61,05; 76,83</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,06; 65,61</t>
+          <t>62,6; 71,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,88; 70,78</t>
+          <t>59,49; 67,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,56; 66,87</t>
+          <t>62,45; 68,71</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,72%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,41; 70,97</t>
+          <t>58,89; 71,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57,34; 70,74</t>
+          <t>59,12; 72,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,3; 69,54</t>
+          <t>61,48; 70,43</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53,73; 66,3</t>
+          <t>63,43; 70,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,13; 69,39</t>
+          <t>61,84; 68,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,09; 66,92</t>
+          <t>63,44; 68,27</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34767</t>
+          <t>37130</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39128</t>
+          <t>31764</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73895</t>
+          <t>68894</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22715; 42137</t>
+          <t>31388; 42844</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31788; 44929</t>
+          <t>26280; 36621</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59580; 83871</t>
+          <t>60815; 76535</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>400</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>272570</t>
+          <t>312675</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>336473</t>
+          <t>271868</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>609043</t>
+          <t>584544</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>221649; 296448</t>
+          <t>291968; 331239</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>312647; 357598</t>
+          <t>252646; 286691</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>541331; 639984</t>
+          <t>556460; 612242</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>147</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>95262</t>
+          <t>109197</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>116886</t>
+          <t>97064</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>212148</t>
+          <t>206261</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>85383; 103743</t>
+          <t>98157; 119349</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>103864; 128143</t>
+          <t>86989; 106551</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>197372; 227614</t>
+          <t>192947; 221028</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>593</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>402600</t>
+          <t>459003</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>492487</t>
+          <t>400696</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>895087</t>
+          <t>859699</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>350163; 432082</t>
+          <t>435647; 481165</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>462686; 516775</t>
+          <t>382002; 421549</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>839121; 934456</t>
+          <t>827558; 890571</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM02_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_R_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman una 2ª pieza de fruta diaria o verduras frescas o cocinadas más de una vez al día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>69,12%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>69,19%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>69,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>58,43; 79,76</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>57,25; 79,77</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>61,05; 76,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>67,04%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>64,02%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>65,6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>62,6; 71,02</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>59,49; 67,51</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>62,45; 68,71</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>65,51%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>65,97%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>65,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>58,89; 71,6</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>59,12; 72,41</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>61,48; 70,43</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>64,87%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>65,9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>63,43; 70,06</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>61,84; 68,24</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63,44; 68,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6912489338762957</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.6919495590188421</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.691571782739809</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>37130</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>31764</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>68894</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.584343323090324</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.5724799210540524</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.6104648343665442</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>31388; 42844</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>26280; 36621</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>60815; 76535</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7976136745719467</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7977499612479296</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7682706877359442</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.6703680679068771</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.6401924097509577</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6559872625425803</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>312675</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>271868</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>584544</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.6259734999929384</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.5949288293646646</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.624471695987404</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>291968; 331239</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>252646; 286691</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>556460; 612242</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.7101693037681245</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.6750965627559282</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.68707038355079</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.6551088912907987</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.6596716243008518</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6572481682453553</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>109197</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>97064</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>206261</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.5888723334787624</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.591199940140809</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.6148244570808689</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>98157; 119349</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>86989; 106551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>192947; 221028</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.7160083479093946</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.724149588639028</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.7043031937129566</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.6682978498137183</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.6486786884473154</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6590079695386417</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>459003</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>400696</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>859699</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.6342913599103251</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.6184155285158994</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.6343701076213252</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>435647; 481165</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>382002; 421549</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>827558; 890571</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.7005650024241967</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.6824365534011096</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.6826732642290977</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman una 2ª pieza de fruta diaria o verduras frescas o cocinadas más de una vez al día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>37130</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>31764</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>68894</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>31388</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>26280</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>60815</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>42844</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>36621</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>76535</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>419</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>312675</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>271868</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>584544</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>291968</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>252646</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>556460</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>331239</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>286691</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>612242</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>147</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>109197</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>97064</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>206261</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>98157</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>86989</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>192947</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>119349</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>106551</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>221028</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>626</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>593</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>459003</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>400696</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>859699</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>435647</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>382002</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>827558</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>481165</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>421549</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>890571</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>